--- a/data/trans_orig/P14B23-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P14B23-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya depresión o ansiedad le limita en 2012</t>
+          <t>Población cuya depresión o ansiedad le limita en 2012 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4684</t>
+          <t>4779</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17226</t>
+          <t>17768</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16741</t>
+          <t>17707</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37555</t>
+          <t>37418</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25161</t>
+          <t>25456</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48935</t>
+          <t>49231</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>277512</t>
+          <t>276970</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>290054</t>
+          <t>289959</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>248599</t>
+          <t>248736</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>269413</t>
+          <t>268447</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>531957</t>
+          <t>531661</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>555731</t>
+          <t>555436</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8813</t>
+          <t>8346</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29570</t>
+          <t>29744</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40478</t>
+          <t>41515</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70024</t>
+          <t>69992</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>54768</t>
+          <t>54596</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>89804</t>
+          <t>90532</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>475957</t>
+          <t>475783</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>496714</t>
+          <t>497181</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>453741</t>
+          <t>453773</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>483287</t>
+          <t>482250</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>939488</t>
+          <t>938760</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>974524</t>
+          <t>974696</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,7%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4864</t>
+          <t>4898</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17354</t>
+          <t>16663</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13766</t>
+          <t>13641</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33029</t>
+          <t>30937</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21854</t>
+          <t>21368</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43237</t>
+          <t>44465</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>306692</t>
+          <t>307383</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>319182</t>
+          <t>319148</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>306954</t>
+          <t>309046</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>326217</t>
+          <t>326342</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>620792</t>
+          <t>619564</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>642175</t>
+          <t>642661</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,78%</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7521</t>
+          <t>7206</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23241</t>
+          <t>23834</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45026</t>
+          <t>46636</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24530</t>
+          <t>23032</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48136</t>
+          <t>48061</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>366461</t>
+          <t>366776</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>340098</t>
+          <t>338488</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>361883</t>
+          <t>361290</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>710970</t>
+          <t>711045</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>734576</t>
+          <t>736074</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,97%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14203</t>
+          <t>15117</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25595</t>
+          <t>25886</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48142</t>
+          <t>47397</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31110</t>
+          <t>31719</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55713</t>
+          <t>57268</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>198415</t>
+          <t>197501</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>209589</t>
+          <t>209573</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>171449</t>
+          <t>172194</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>193996</t>
+          <t>193705</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>376496</t>
+          <t>374941</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>401099</t>
+          <t>400490</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,66%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4299</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17123</t>
+          <t>16618</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15396</t>
+          <t>16243</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33664</t>
+          <t>34932</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22808</t>
+          <t>22342</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>44919</t>
+          <t>44403</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>256858</t>
+          <t>257363</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>269682</t>
+          <t>269929</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>244432</t>
+          <t>243164</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>262700</t>
+          <t>261853</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>507158</t>
+          <t>507674</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>529269</t>
+          <t>529735</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,95%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9798</t>
+          <t>9900</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27456</t>
+          <t>26882</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29072</t>
+          <t>28021</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55848</t>
+          <t>53924</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>42983</t>
+          <t>43581</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>73493</t>
+          <t>73887</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>635332</t>
+          <t>635906</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>652990</t>
+          <t>652888</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>636952</t>
+          <t>638876</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>663728</t>
+          <t>664779</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1282095</t>
+          <t>1281701</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1312605</t>
+          <t>1312007</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,79%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8232</t>
+          <t>8177</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26060</t>
+          <t>24533</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>37491</t>
+          <t>37060</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>64618</t>
+          <t>66017</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>49990</t>
+          <t>49997</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>84656</t>
+          <t>81122</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>750889</t>
+          <t>752416</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>768717</t>
+          <t>768772</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>756832</t>
+          <t>755433</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>783959</t>
+          <t>784390</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1513743</t>
+          <t>1517277</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1548409</t>
+          <t>1548402</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>68163</t>
+          <t>67656</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>107992</t>
+          <t>107473</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>253008</t>
+          <t>251793</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>319642</t>
+          <t>317833</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>333642</t>
+          <t>336930</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>406157</t>
+          <t>414637</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3316638</t>
+          <t>3317157</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3356467</t>
+          <t>3356974</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3227321</t>
+          <t>3229130</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3293955</t>
+          <t>3295170</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6565435</t>
+          <t>6556955</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6637950</t>
+          <t>6634662</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,17%</t>
         </is>
       </c>
     </row>
@@ -3860,7 +3860,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya depresión o ansiedad le limita en 2016</t>
+          <t>Población cuya depresión o ansiedad le limita en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3462</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15953</t>
+          <t>16019</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21090</t>
+          <t>20971</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43287</t>
+          <t>44933</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27074</t>
+          <t>26907</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52923</t>
+          <t>53167</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>277808</t>
+          <t>277742</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>290429</t>
+          <t>290299</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>245416</t>
+          <t>243770</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>267613</t>
+          <t>267732</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>529541</t>
+          <t>529297</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>555390</t>
+          <t>555557</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7310</t>
+          <t>7544</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22676</t>
+          <t>22828</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31606</t>
+          <t>32204</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58557</t>
+          <t>58542</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44442</t>
+          <t>44352</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>75685</t>
+          <t>74340</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>479899</t>
+          <t>479747</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>495265</t>
+          <t>495031</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>464527</t>
+          <t>464542</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>491478</t>
+          <t>490880</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>949974</t>
+          <t>951319</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>981217</t>
+          <t>981307</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>934</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7586</t>
+          <t>7621</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11323</t>
+          <t>11092</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27747</t>
+          <t>27648</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13611</t>
+          <t>13143</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32606</t>
+          <t>31405</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>310979</t>
+          <t>310944</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317632</t>
+          <t>317631</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>308562</t>
+          <t>308661</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>324986</t>
+          <t>325217</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>622268</t>
+          <t>623469</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>641263</t>
+          <t>641731</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,99%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10930</t>
+          <t>11272</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10930</t>
+          <t>10873</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27868</t>
+          <t>27488</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14739</t>
+          <t>15622</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34563</t>
+          <t>34208</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>359034</t>
+          <t>358692</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>368881</t>
+          <t>368029</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>359415</t>
+          <t>359795</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>376353</t>
+          <t>376410</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>722684</t>
+          <t>723039</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>742508</t>
+          <t>741625</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5618</t>
+          <t>5685</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18767</t>
+          <t>17906</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11400</t>
+          <t>10650</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27247</t>
+          <t>26778</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20489</t>
+          <t>19961</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39739</t>
+          <t>39502</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>192454</t>
+          <t>193315</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>205603</t>
+          <t>205536</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>191340</t>
+          <t>191809</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>207187</t>
+          <t>207937</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>390069</t>
+          <t>390306</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>409319</t>
+          <t>409847</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,36%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>791</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6850</t>
+          <t>7308</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18689</t>
+          <t>18132</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>38195</t>
+          <t>37781</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20355</t>
+          <t>19563</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>41474</t>
+          <t>41434</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>256273</t>
+          <t>255815</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262334</t>
+          <t>262332</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>234920</t>
+          <t>235334</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>254426</t>
+          <t>254983</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>494764</t>
+          <t>494804</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>515883</t>
+          <t>516675</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,35%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2751</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15934</t>
+          <t>16483</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19337</t>
+          <t>19522</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42369</t>
+          <t>42095</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>24671</t>
+          <t>24435</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>51598</t>
+          <t>50832</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>640624</t>
+          <t>640075</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>653807</t>
+          <t>653432</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>648925</t>
+          <t>649199</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>671957</t>
+          <t>671772</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1296254</t>
+          <t>1297020</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1323181</t>
+          <t>1323417</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10536</t>
+          <t>9594</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26311</t>
+          <t>25969</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>39331</t>
+          <t>40778</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>68167</t>
+          <t>70539</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>54099</t>
+          <t>53389</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>87243</t>
+          <t>88287</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>752272</t>
+          <t>752614</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>768047</t>
+          <t>768989</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>758000</t>
+          <t>755628</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>786836</t>
+          <t>785389</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1517507</t>
+          <t>1516463</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1550651</t>
+          <t>1551361</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,67%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>53009</t>
+          <t>51745</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>85211</t>
+          <t>84366</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>208193</t>
+          <t>206790</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>268155</t>
+          <t>268244</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>270864</t>
+          <t>273416</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>340407</t>
+          <t>340593</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3309139</t>
+          <t>3309984</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3341341</t>
+          <t>3342605</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3276387</t>
+          <t>3276298</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3336349</t>
+          <t>3337752</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6598485</t>
+          <t>6598299</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6668028</t>
+          <t>6665476</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,06%</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya depresión o ansiedad le limita en 2023</t>
+          <t>Población cuya depresión o ansiedad le limita en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7378,12 +7378,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>1671</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>9871</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8648</t>
+          <t>8840</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18338</t>
+          <t>18361</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11996</t>
+          <t>12402</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25559</t>
+          <t>24805</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -7491,12 +7491,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>300729</t>
+          <t>301572</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>309773</t>
+          <t>309772</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>271297</t>
+          <t>271274</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>280987</t>
+          <t>280795</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>575518</t>
+          <t>576272</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>589081</t>
+          <t>588675</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -7721,12 +7721,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12257</t>
+          <t>12415</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31521</t>
+          <t>32614</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44310</t>
+          <t>44356</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66704</t>
+          <t>66636</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>61517</t>
+          <t>61654</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>93328</t>
+          <t>92769</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>486869</t>
+          <t>485776</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>506133</t>
+          <t>505975</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>448265</t>
+          <t>448333</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>470659</t>
+          <t>470613</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>940031</t>
+          <t>940590</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>971842</t>
+          <t>971705</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,03%</t>
         </is>
       </c>
     </row>
@@ -8064,12 +8064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11271</t>
+          <t>11913</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28215</t>
+          <t>28170</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8079,12 +8079,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16436</t>
+          <t>16069</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30954</t>
+          <t>28976</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8114,12 +8114,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30871</t>
+          <t>30024</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52477</t>
+          <t>51513</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -8177,12 +8177,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>287835</t>
+          <t>287880</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>304779</t>
+          <t>304137</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8192,12 +8192,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>318174</t>
+          <t>320152</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>332692</t>
+          <t>333059</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>612701</t>
+          <t>613665</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>634307</t>
+          <t>635154</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8262,12 +8262,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -8407,12 +8407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9597</t>
+          <t>8801</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28291</t>
+          <t>25896</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8422,12 +8422,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18654</t>
+          <t>19619</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47074</t>
+          <t>46682</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8457,12 +8457,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34288</t>
+          <t>35259</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65247</t>
+          <t>64637</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -8520,12 +8520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>284266</t>
+          <t>286661</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>302960</t>
+          <t>303756</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8535,12 +8535,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>428644</t>
+          <t>429036</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>457064</t>
+          <t>456099</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8570,12 +8570,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>723027</t>
+          <t>723637</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>753986</t>
+          <t>753015</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,53%</t>
         </is>
       </c>
     </row>
@@ -8750,12 +8750,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>590</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5794</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8785,12 +8785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>4752</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14394</t>
+          <t>14692</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8800,12 +8800,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7119</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17273</t>
+          <t>17158</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -8863,12 +8863,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>172948</t>
+          <t>173396</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178094</t>
+          <t>178152</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8898,12 +8898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>244385</t>
+          <t>244087</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>254190</t>
+          <t>254027</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8913,12 +8913,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>420248</t>
+          <t>420363</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>430402</t>
+          <t>430321</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -9093,12 +9093,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9427</t>
+          <t>9602</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23045</t>
+          <t>22329</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12879</t>
+          <t>12877</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25583</t>
+          <t>24967</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25028</t>
+          <t>24408</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>44074</t>
+          <t>42753</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -9206,12 +9206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>246591</t>
+          <t>247307</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260209</t>
+          <t>260034</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>231473</t>
+          <t>232089</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>244177</t>
+          <t>244179</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>482618</t>
+          <t>483939</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>501664</t>
+          <t>502284</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,37%</t>
         </is>
       </c>
     </row>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20485</t>
+          <t>20084</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44456</t>
+          <t>44385</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30669</t>
+          <t>31012</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>93471</t>
+          <t>95039</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>56890</t>
+          <t>61420</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>121928</t>
+          <t>122980</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -9549,12 +9549,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>579823</t>
+          <t>579894</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>603794</t>
+          <t>604195</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9584,12 +9584,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>755794</t>
+          <t>754226</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>818596</t>
+          <t>818253</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1351616</t>
+          <t>1350564</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1416654</t>
+          <t>1412124</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>95,83%</t>
         </is>
       </c>
     </row>
@@ -9779,12 +9779,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6680</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>28355</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>39554</t>
+          <t>40353</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>62088</t>
+          <t>62282</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>41964</t>
+          <t>42618</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>87685</t>
+          <t>88368</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -9892,12 +9892,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>900365</t>
+          <t>898413</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>922040</t>
+          <t>921475</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9907,12 +9907,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>655643</t>
+          <t>655449</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>678177</t>
+          <t>677378</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1558767</t>
+          <t>1558084</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1604488</t>
+          <t>1603834</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,41%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>97311</t>
+          <t>95568</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>153069</t>
+          <t>151131</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>214393</t>
+          <t>217540</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>300328</t>
+          <t>301198</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>344408</t>
+          <t>345309</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>437020</t>
+          <t>440752</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3306748</t>
+          <t>3308686</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3362506</t>
+          <t>3364249</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3411952</t>
+          <t>3411082</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3497887</t>
+          <t>3494740</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6735077</t>
+          <t>6731345</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6827689</t>
+          <t>6826788</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,19%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P14B23-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P14B23-Provincia-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4779</t>
+          <t>4321</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17768</t>
+          <t>17230</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17707</t>
+          <t>17450</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37418</t>
+          <t>37013</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25456</t>
+          <t>25309</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49231</t>
+          <t>48544</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>276970</t>
+          <t>277508</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>289959</t>
+          <t>290417</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>248736</t>
+          <t>249141</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>268447</t>
+          <t>268704</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>531661</t>
+          <t>532348</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>555436</t>
+          <t>555583</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,64%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8346</t>
+          <t>8166</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29744</t>
+          <t>28711</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41515</t>
+          <t>41308</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69992</t>
+          <t>70721</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>54596</t>
+          <t>54149</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>90532</t>
+          <t>90109</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>475783</t>
+          <t>476816</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>497181</t>
+          <t>497361</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>453773</t>
+          <t>453044</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>482250</t>
+          <t>482457</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>938760</t>
+          <t>939183</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>974696</t>
+          <t>975143</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,74%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4898</t>
+          <t>5690</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16663</t>
+          <t>17789</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13641</t>
+          <t>14003</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30937</t>
+          <t>34050</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21368</t>
+          <t>21868</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44465</t>
+          <t>42397</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>307383</t>
+          <t>306257</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>319148</t>
+          <t>318356</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>309046</t>
+          <t>305933</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>326342</t>
+          <t>325980</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>619564</t>
+          <t>621632</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>642661</t>
+          <t>642161</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,71%</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7206</t>
+          <t>6674</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23834</t>
+          <t>22847</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46636</t>
+          <t>45718</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23032</t>
+          <t>25323</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48061</t>
+          <t>49002</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>366776</t>
+          <t>367308</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>338488</t>
+          <t>339406</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>361290</t>
+          <t>362277</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>711045</t>
+          <t>710104</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>736074</t>
+          <t>733783</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15117</t>
+          <t>14084</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25886</t>
+          <t>25761</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47397</t>
+          <t>47598</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31719</t>
+          <t>31154</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57268</t>
+          <t>55476</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>12,84%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>197501</t>
+          <t>198534</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>209573</t>
+          <t>209459</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>172194</t>
+          <t>171993</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>193705</t>
+          <t>193830</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>374941</t>
+          <t>376733</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>400490</t>
+          <t>401055</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,79%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4052</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16618</t>
+          <t>16974</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16243</t>
+          <t>15534</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34932</t>
+          <t>34350</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22342</t>
+          <t>23155</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>44403</t>
+          <t>45466</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>257363</t>
+          <t>257007</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>269929</t>
+          <t>269857</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>243164</t>
+          <t>243746</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>261853</t>
+          <t>262562</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>507674</t>
+          <t>506611</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>529735</t>
+          <t>528922</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9900</t>
+          <t>10071</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26882</t>
+          <t>28612</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28021</t>
+          <t>28975</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53924</t>
+          <t>53395</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>43581</t>
+          <t>43119</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>73887</t>
+          <t>73582</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>635906</t>
+          <t>634176</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>652888</t>
+          <t>652717</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>638876</t>
+          <t>639405</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>664779</t>
+          <t>663825</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1281701</t>
+          <t>1282006</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1312007</t>
+          <t>1312469</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8177</t>
+          <t>8189</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24533</t>
+          <t>24409</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>37060</t>
+          <t>37580</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>66017</t>
+          <t>65440</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>49997</t>
+          <t>50784</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>81122</t>
+          <t>85540</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>752416</t>
+          <t>752540</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>768772</t>
+          <t>768760</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>755433</t>
+          <t>756010</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>784390</t>
+          <t>783870</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1517277</t>
+          <t>1512859</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1548402</t>
+          <t>1547615</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>67656</t>
+          <t>69133</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>107473</t>
+          <t>108333</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>251793</t>
+          <t>255069</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>317833</t>
+          <t>317908</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>336930</t>
+          <t>334280</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>414637</t>
+          <t>407596</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3317157</t>
+          <t>3316297</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3356974</t>
+          <t>3355497</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3229130</t>
+          <t>3229055</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3295170</t>
+          <t>3291894</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6556955</t>
+          <t>6563996</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6634662</t>
+          <t>6637312</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,21%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3462</t>
+          <t>3025</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16019</t>
+          <t>14842</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20971</t>
+          <t>21669</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44933</t>
+          <t>43755</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26907</t>
+          <t>27245</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53167</t>
+          <t>56300</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>277742</t>
+          <t>278919</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>290299</t>
+          <t>290736</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>243770</t>
+          <t>244948</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>267732</t>
+          <t>267034</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>529297</t>
+          <t>526164</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>555557</t>
+          <t>555219</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,32%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7544</t>
+          <t>7441</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22828</t>
+          <t>22331</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32204</t>
+          <t>31751</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58542</t>
+          <t>58643</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44352</t>
+          <t>44130</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74340</t>
+          <t>75601</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>479747</t>
+          <t>480244</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>495031</t>
+          <t>495134</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>464542</t>
+          <t>464441</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>490880</t>
+          <t>491333</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>951319</t>
+          <t>950058</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>981307</t>
+          <t>981529</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,7%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>933</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7621</t>
+          <t>7785</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11092</t>
+          <t>10772</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27648</t>
+          <t>28457</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13143</t>
+          <t>13888</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31405</t>
+          <t>33168</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>310944</t>
+          <t>310780</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317631</t>
+          <t>317632</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>308661</t>
+          <t>307852</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>325217</t>
+          <t>325537</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>623469</t>
+          <t>621706</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>641731</t>
+          <t>640986</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1935</t>
+          <t>1849</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11272</t>
+          <t>10881</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10873</t>
+          <t>10611</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27488</t>
+          <t>27381</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15622</t>
+          <t>15647</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34208</t>
+          <t>34216</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>358692</t>
+          <t>359083</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>368029</t>
+          <t>368115</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>359795</t>
+          <t>359902</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>376410</t>
+          <t>376672</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>723039</t>
+          <t>723031</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>741625</t>
+          <t>741600</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5685</t>
+          <t>4964</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17906</t>
+          <t>17358</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10650</t>
+          <t>11516</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26778</t>
+          <t>27283</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19961</t>
+          <t>19914</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39502</t>
+          <t>39599</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>193315</t>
+          <t>193863</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>205536</t>
+          <t>206257</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>191809</t>
+          <t>191304</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>207937</t>
+          <t>207071</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>390306</t>
+          <t>390209</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>409847</t>
+          <t>409894</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,37%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>795</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7308</t>
+          <t>7446</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18132</t>
+          <t>17463</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37781</t>
+          <t>37488</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19563</t>
+          <t>19279</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>41434</t>
+          <t>42721</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>255815</t>
+          <t>255677</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262332</t>
+          <t>262328</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>235334</t>
+          <t>235627</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>254983</t>
+          <t>255652</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>494804</t>
+          <t>493517</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>516675</t>
+          <t>516959</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,4%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3126</t>
+          <t>2949</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16483</t>
+          <t>15473</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19522</t>
+          <t>19449</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42095</t>
+          <t>42355</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>24435</t>
+          <t>25430</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>50832</t>
+          <t>51983</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>640075</t>
+          <t>641085</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>653432</t>
+          <t>653609</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>649199</t>
+          <t>648939</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>671772</t>
+          <t>671845</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1297020</t>
+          <t>1295869</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1323417</t>
+          <t>1322422</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9594</t>
+          <t>10478</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>25969</t>
+          <t>26659</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>40778</t>
+          <t>39485</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>70539</t>
+          <t>69036</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>53389</t>
+          <t>54091</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>88287</t>
+          <t>88516</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>752614</t>
+          <t>751924</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>768989</t>
+          <t>768105</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>755628</t>
+          <t>757131</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>785389</t>
+          <t>786682</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1516463</t>
+          <t>1516234</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1551361</t>
+          <t>1550659</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,63%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>51745</t>
+          <t>51778</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>84366</t>
+          <t>86034</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>206790</t>
+          <t>207921</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>268244</t>
+          <t>270549</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>273416</t>
+          <t>271816</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>340593</t>
+          <t>345097</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3309984</t>
+          <t>3308316</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3342605</t>
+          <t>3342572</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3276298</t>
+          <t>3273993</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3337752</t>
+          <t>3336621</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6598299</t>
+          <t>6593795</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6665476</t>
+          <t>6667076</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,08%</t>
         </is>
       </c>
     </row>
@@ -7373,32 +7373,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4679</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1671</t>
+          <t>1628</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9871</t>
+          <t>9630</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7408,32 +7408,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13010</t>
+          <t>13937</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8840</t>
+          <t>9602</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18361</t>
+          <t>20323</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7443,32 +7443,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>17689</t>
+          <t>18264</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12402</t>
+          <t>12935</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24805</t>
+          <t>26009</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -7486,32 +7486,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>306764</t>
+          <t>314518</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>301572</t>
+          <t>309215</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>309772</t>
+          <t>317217</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7521,32 +7521,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>276625</t>
+          <t>302124</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>271274</t>
+          <t>295738</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>280795</t>
+          <t>306459</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7556,32 +7556,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>583388</t>
+          <t>616642</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>576272</t>
+          <t>608897</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>588675</t>
+          <t>621971</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -7599,17 +7599,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7634,17 +7634,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7669,17 +7669,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7716,32 +7716,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20814</t>
+          <t>21298</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12415</t>
+          <t>13196</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32614</t>
+          <t>32355</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7751,32 +7751,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>54756</t>
+          <t>58995</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44356</t>
+          <t>48133</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66636</t>
+          <t>72438</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7786,32 +7786,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>75570</t>
+          <t>80293</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>61654</t>
+          <t>66031</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>92769</t>
+          <t>98538</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -7829,32 +7829,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>497576</t>
+          <t>509349</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>485776</t>
+          <t>498292</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>505975</t>
+          <t>517451</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7864,32 +7864,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>460213</t>
+          <t>487499</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>448333</t>
+          <t>474056</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>470613</t>
+          <t>498361</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7899,32 +7899,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>957789</t>
+          <t>996848</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>940590</t>
+          <t>978603</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>971705</t>
+          <t>1011110</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,87%</t>
         </is>
       </c>
     </row>
@@ -7942,17 +7942,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7977,17 +7977,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8012,17 +8012,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8059,32 +8059,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>18472</t>
+          <t>17926</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11913</t>
+          <t>10841</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28170</t>
+          <t>26850</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8094,32 +8094,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>22170</t>
+          <t>23207</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16069</t>
+          <t>17129</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28976</t>
+          <t>32077</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8129,32 +8129,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>40642</t>
+          <t>41133</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30024</t>
+          <t>31953</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51513</t>
+          <t>52777</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -8172,32 +8172,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>297578</t>
+          <t>298067</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>287880</t>
+          <t>289143</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>304137</t>
+          <t>305152</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8207,32 +8207,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>326958</t>
+          <t>333174</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>320152</t>
+          <t>324304</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>333059</t>
+          <t>339252</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8242,32 +8242,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>624536</t>
+          <t>631242</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>613665</t>
+          <t>619598</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>635154</t>
+          <t>640422</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,25%</t>
         </is>
       </c>
     </row>
@@ -8285,17 +8285,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8355,17 +8355,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8402,32 +8402,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16227</t>
+          <t>17442</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8801</t>
+          <t>9940</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25896</t>
+          <t>29715</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8437,32 +8437,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>33609</t>
+          <t>36178</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19619</t>
+          <t>27724</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46682</t>
+          <t>47040</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8472,32 +8472,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>49836</t>
+          <t>53620</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35259</t>
+          <t>42441</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64637</t>
+          <t>68869</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -8515,32 +8515,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>296330</t>
+          <t>355703</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>286661</t>
+          <t>343430</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>303756</t>
+          <t>363205</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8550,32 +8550,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>442109</t>
+          <t>385783</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>429036</t>
+          <t>374921</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>456099</t>
+          <t>394237</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8585,32 +8585,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>738438</t>
+          <t>741487</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>723637</t>
+          <t>726238</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>753015</t>
+          <t>752666</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>94,66%</t>
         </is>
       </c>
     </row>
@@ -8628,17 +8628,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8663,17 +8663,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8698,17 +8698,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8745,32 +8745,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2390</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>545</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5346</t>
+          <t>5783</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8780,32 +8780,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>9851</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4752</t>
+          <t>6597</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14692</t>
+          <t>14518</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8815,32 +8815,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>11689</t>
+          <t>12240</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>8192</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17158</t>
+          <t>18035</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -8858,32 +8858,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>176441</t>
+          <t>203275</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>173396</t>
+          <t>199882</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178152</t>
+          <t>205120</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8893,32 +8893,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>249391</t>
+          <t>219067</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>244087</t>
+          <t>214400</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>254027</t>
+          <t>222321</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8928,32 +8928,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>425832</t>
+          <t>422342</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>420363</t>
+          <t>416547</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>430321</t>
+          <t>426390</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -8971,17 +8971,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9006,17 +9006,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9041,17 +9041,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9088,32 +9088,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14896</t>
+          <t>14465</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9602</t>
+          <t>9142</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22329</t>
+          <t>21942</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9123,32 +9123,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18060</t>
+          <t>18560</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12877</t>
+          <t>12737</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24967</t>
+          <t>25712</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9158,32 +9158,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>32955</t>
+          <t>33024</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24408</t>
+          <t>25112</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>42753</t>
+          <t>42560</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -9201,32 +9201,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>254740</t>
+          <t>256242</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>247307</t>
+          <t>248765</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260034</t>
+          <t>261565</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9236,32 +9236,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>238996</t>
+          <t>245190</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>232089</t>
+          <t>238038</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>244179</t>
+          <t>251013</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9271,32 +9271,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>493737</t>
+          <t>501433</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>483939</t>
+          <t>491897</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>502284</t>
+          <t>509345</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,3%</t>
         </is>
       </c>
     </row>
@@ -9314,17 +9314,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9349,17 +9349,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9384,17 +9384,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9431,32 +9431,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>30309</t>
+          <t>35675</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20084</t>
+          <t>23526</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44385</t>
+          <t>51435</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9466,32 +9466,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>66943</t>
+          <t>80759</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31012</t>
+          <t>66196</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>95039</t>
+          <t>97182</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9501,32 +9501,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>97252</t>
+          <t>116434</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>61420</t>
+          <t>95557</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>122980</t>
+          <t>137870</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -9544,32 +9544,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>593970</t>
+          <t>684012</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>579894</t>
+          <t>668252</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>604195</t>
+          <t>696161</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9579,32 +9579,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>782322</t>
+          <t>691298</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>754226</t>
+          <t>674875</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>818253</t>
+          <t>705861</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9614,32 +9614,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1376292</t>
+          <t>1375310</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1350564</t>
+          <t>1353874</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1412124</t>
+          <t>1396187</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>93,59%</t>
         </is>
       </c>
     </row>
@@ -9657,17 +9657,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9692,17 +9692,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9727,17 +9727,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9774,32 +9774,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>18105</t>
+          <t>21696</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7245</t>
+          <t>13829</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>32167</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9809,32 +9809,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>50495</t>
+          <t>57844</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>40353</t>
+          <t>46334</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>62282</t>
+          <t>71233</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9844,32 +9844,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>68600</t>
+          <t>79540</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>42618</t>
+          <t>65337</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>88368</t>
+          <t>95119</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -9887,32 +9887,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>910615</t>
+          <t>776376</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>898413</t>
+          <t>765905</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>921475</t>
+          <t>784243</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9922,32 +9922,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>667236</t>
+          <t>773487</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>655449</t>
+          <t>760098</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>677378</t>
+          <t>784997</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9957,32 +9957,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1577852</t>
+          <t>1549863</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1558084</t>
+          <t>1534284</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1603834</t>
+          <t>1564066</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>95,99%</t>
         </is>
       </c>
     </row>
@@ -10000,17 +10000,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10035,17 +10035,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10070,17 +10070,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10117,32 +10117,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>125802</t>
+          <t>135218</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>95568</t>
+          <t>110878</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>151131</t>
+          <t>160747</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10152,32 +10152,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>268431</t>
+          <t>299330</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>217540</t>
+          <t>272183</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>301198</t>
+          <t>328950</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10187,32 +10187,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>394233</t>
+          <t>434548</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>345309</t>
+          <t>394765</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>440752</t>
+          <t>470025</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -10230,32 +10230,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3334015</t>
+          <t>3397544</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3308686</t>
+          <t>3372015</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3364249</t>
+          <t>3421884</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10265,32 +10265,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3443849</t>
+          <t>3437624</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3411082</t>
+          <t>3408004</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3494740</t>
+          <t>3464771</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10300,32 +10300,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6777864</t>
+          <t>6835168</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6731345</t>
+          <t>6799691</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6826788</t>
+          <t>6874951</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>94,57%</t>
         </is>
       </c>
     </row>
@@ -10343,17 +10343,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10378,17 +10378,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10413,17 +10413,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
